--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T15:00:26+00:00</t>
+    <t>2026-03-31T13:26:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T13:26:33+00:00</t>
+    <t>2026-04-09T09:14:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:14:18+00:00</t>
+    <t>2026-04-09T09:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
+++ b/sfe-lot-3-serafin/ig/StructureDefinition-tddui-entry-date-origin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:18:02+00:00</t>
+    <t>2026-04-24T09:04:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
